--- a/tests/ITER_2D_APEC_fine2/input_template.xlsx
+++ b/tests/ITER_2D_APEC_fine2/input_template.xlsx
@@ -964,22 +964,22 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
@@ -996,22 +996,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
@@ -1037,13 +1037,13 @@
         <v>8e-07</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
@@ -1069,13 +1069,13 @@
         <v>1e-08</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
